--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.07751937984496124</v>
+        <v>0.06015037593984962</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1276595744680851</v>
+        <v>0.09859154929577464</v>
       </c>
       <c r="D2">
-        <v>0.924812030075188</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="E2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.06015037593984962</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.09859154929577464</v>
+        <v>0.09154929577464789</v>
       </c>
       <c r="D2">
-        <v>0.9411764705882353</v>
+        <v>0.9485294117647058</v>
       </c>
       <c r="E2">
         <v>133</v>
